--- a/Peter/Sectoral Analysis (ISIC)/ISIC3/ISIC3_tidied.xlsx
+++ b/Peter/Sectoral Analysis (ISIC)/ISIC3/ISIC3_tidied.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Bede7/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Bede7/Desktop/RA/rproj-NatlAccountsSectorData/Peter/Sectoral Analysis (ISIC)/ISIC3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F46AE0E7-91A1-0947-9088-94D5F31E9A6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DAE1BAE-63B7-354A-9048-1DA181B2BF3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="14660" windowHeight="16560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="14660" windowHeight="16560" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -234,9 +234,6 @@
     <t>vatu</t>
   </si>
   <si>
-    <t>Agriculture</t>
-  </si>
-  <si>
     <t>Construction</t>
   </si>
   <si>
@@ -289,6 +286,9 @@
   </si>
   <si>
     <t>sector sum</t>
+  </si>
+  <si>
+    <t>Primary Sector</t>
   </si>
 </sst>
 </file>
@@ -647,34 +647,34 @@
         <v>2</v>
       </c>
       <c r="D1" t="s">
+        <v>84</v>
+      </c>
+      <c r="E1" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" t="s">
         <v>66</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>68</v>
       </c>
-      <c r="F1" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>69</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
+        <v>74</v>
+      </c>
+      <c r="J1" t="s">
         <v>70</v>
       </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
+        <v>76</v>
+      </c>
+      <c r="L1" t="s">
         <v>75</v>
       </c>
-      <c r="J1" t="s">
-        <v>71</v>
-      </c>
-      <c r="K1" t="s">
-        <v>77</v>
-      </c>
-      <c r="L1" t="s">
-        <v>76</v>
-      </c>
       <c r="M1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.2">
@@ -27354,60 +27354,60 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C1" t="s">
         <v>66</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>68</v>
       </c>
-      <c r="C1" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>69</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
+        <v>74</v>
+      </c>
+      <c r="G1" t="s">
         <v>70</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
+        <v>76</v>
+      </c>
+      <c r="I1" t="s">
         <v>75</v>
-      </c>
-      <c r="G1" t="s">
-        <v>71</v>
-      </c>
-      <c r="H1" t="s">
-        <v>77</v>
-      </c>
-      <c r="I1" t="s">
-        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
+        <v>71</v>
+      </c>
+      <c r="B2" t="s">
         <v>72</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>73</v>
       </c>
-      <c r="C2" t="s">
-        <v>74</v>
-      </c>
       <c r="D2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E2" t="s">
         <v>78</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>79</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>80</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I2" t="s">
         <v>81</v>
-      </c>
-      <c r="H2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I2" t="s">
-        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/Peter/Sectoral Analysis (ISIC)/ISIC3/ISIC3_tidied.xlsx
+++ b/Peter/Sectoral Analysis (ISIC)/ISIC3/ISIC3_tidied.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Bede7/Desktop/RA/rproj-NatlAccountsSectorData/Peter/Sectoral Analysis (ISIC)/ISIC3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DAE1BAE-63B7-354A-9048-1DA181B2BF3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{428CD6FC-1B60-0343-9D3D-E0229D5B753C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="740" windowWidth="14660" windowHeight="16560" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5440" yWindow="740" windowWidth="18420" windowHeight="16560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -668,10 +668,10 @@
         <v>70</v>
       </c>
       <c r="K1" t="s">
+        <v>75</v>
+      </c>
+      <c r="L1" t="s">
         <v>76</v>
-      </c>
-      <c r="L1" t="s">
-        <v>75</v>
       </c>
       <c r="M1" t="s">
         <v>83</v>
@@ -27375,10 +27375,10 @@
         <v>70</v>
       </c>
       <c r="H1" t="s">
+        <v>75</v>
+      </c>
+      <c r="I1" t="s">
         <v>76</v>
-      </c>
-      <c r="I1" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
